--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784711</v>
+        <v>136857358</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415319</v>
+        <v>415209</v>
       </c>
       <c r="R3" t="n">
-        <v>6971444</v>
+        <v>6971379</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784711</t>
+          <t>https://artportalen.se/Sighting/136857358</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784710</v>
+        <v>136858141</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415311</v>
+        <v>415242</v>
       </c>
       <c r="R4" t="n">
-        <v>6971457</v>
+        <v>6971390</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,49 +969,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784710</t>
+          <t>https://artportalen.se/Sighting/136858141</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784712</v>
+        <v>135784711</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>92267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415320</v>
+        <v>415319</v>
       </c>
       <c r="R5" t="n">
-        <v>6971460</v>
+        <v>6971444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,16 +1082,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784712</t>
+          <t>https://artportalen.se/Sighting/135784711</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784706</v>
+        <v>136857485</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>91117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415176</v>
+        <v>415221</v>
       </c>
       <c r="R6" t="n">
-        <v>6971428</v>
+        <v>6971377</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Klen gran med helt avskalad bark.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,27 +1173,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784706</t>
+          <t>https://artportalen.se/Sighting/136857485</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784708</v>
+        <v>135784710</v>
       </c>
       <c r="B7" t="n">
-        <v>58154</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415290</v>
+        <v>415311</v>
       </c>
       <c r="R7" t="n">
-        <v>6971459</v>
+        <v>6971457</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,54 +1286,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784708</t>
+          <t>https://artportalen.se/Sighting/135784710</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6794708</v>
+        <v>136857956</v>
       </c>
       <c r="B8" t="n">
-        <v>106229</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415241</v>
+        <v>415209</v>
       </c>
       <c r="R8" t="n">
-        <v>6971543</v>
+        <v>6971392</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,69 +1377,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794708</t>
+          <t>https://artportalen.se/Sighting/136857956</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6794707</v>
+        <v>135784712</v>
       </c>
       <c r="B9" t="n">
-        <v>103683</v>
+        <v>80079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415241</v>
+        <v>415320</v>
       </c>
       <c r="R9" t="n">
-        <v>6971543</v>
+        <v>6971460</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,69 +1479,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794707</t>
+          <t>https://artportalen.se/Sighting/135784712</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6794715</v>
+        <v>135784706</v>
       </c>
       <c r="B10" t="n">
-        <v>104628</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415427</v>
+        <v>415176</v>
       </c>
       <c r="R10" t="n">
-        <v>6971592</v>
+        <v>6971428</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,12 +1561,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Klen gran med helt avskalad bark.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,31 +1586,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794715</t>
+          <t>https://artportalen.se/Sighting/135784706</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784707</v>
+        <v>135784708</v>
       </c>
       <c r="B11" t="n">
-        <v>80050</v>
+        <v>58154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1626,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415199</v>
+        <v>415290</v>
       </c>
       <c r="R11" t="n">
-        <v>6971418</v>
+        <v>6971459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1698,426 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784708</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6794708</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794708</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6794707</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794707</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6794715</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>415427</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971592</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794715</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784707</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>415199</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971418</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784707</t>
         </is>
@@ -1727,6 +2135,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135784709</v>
+        <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>79126</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415301</v>
+        <v>415340</v>
       </c>
       <c r="R2" t="n">
-        <v>6971466</v>
+        <v>6971408</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ev urskogsticka, skickad på mikroskopiering.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784709</t>
+          <t>https://artportalen.se/Sighting/136919563</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136857358</v>
+        <v>135784709</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +818,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vikavan, Vikavan, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415209</v>
+        <v>415301</v>
       </c>
       <c r="R3" t="n">
-        <v>6971379</v>
+        <v>6971466</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,24 +872,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136857358</t>
+          <t>https://artportalen.se/Sighting/135784709</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136858141</v>
+        <v>136857358</v>
       </c>
       <c r="B4" t="n">
         <v>79142</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415242</v>
+        <v>415209</v>
       </c>
       <c r="R4" t="n">
-        <v>6971390</v>
+        <v>6971379</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,54 +985,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858141</t>
+          <t>https://artportalen.se/Sighting/136857358</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784711</v>
+        <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>92267</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415319</v>
+        <v>415242</v>
       </c>
       <c r="R5" t="n">
-        <v>6971444</v>
+        <v>6971390</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1076,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784711</t>
+          <t>https://artportalen.se/Sighting/136858141</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136857485</v>
+        <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>91117</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vikavan, Vikavan, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415221</v>
+        <v>415242</v>
       </c>
       <c r="R6" t="n">
-        <v>6971377</v>
+        <v>6971392</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,16 +1189,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136857485</t>
+          <t>https://artportalen.se/Sighting/136919514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784710</v>
+        <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415311</v>
+        <v>415284</v>
       </c>
       <c r="R7" t="n">
-        <v>6971457</v>
+        <v>6971350</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1280,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784710</t>
+          <t>https://artportalen.se/Sighting/136919516</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136857956</v>
+        <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>79142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikavan, Vikavan, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415209</v>
+        <v>415279</v>
       </c>
       <c r="R8" t="n">
-        <v>6971392</v>
+        <v>6971333</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,16 +1393,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136857956</t>
+          <t>https://artportalen.se/Sighting/136919517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784712</v>
+        <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>80079</v>
+        <v>79142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1410,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415320</v>
+        <v>415274</v>
       </c>
       <c r="R9" t="n">
-        <v>6971460</v>
+        <v>6971314</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1464,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,27 +1484,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784712</t>
+          <t>https://artportalen.se/Sighting/136919521</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784706</v>
+        <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>79142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,37 +1512,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415176</v>
+        <v>415286</v>
       </c>
       <c r="R10" t="n">
-        <v>6971428</v>
+        <v>6971317</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,17 +1566,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Klen gran med helt avskalad bark.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,27 +1586,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784706</t>
+          <t>https://artportalen.se/Sighting/136919522</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784708</v>
+        <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>58154</v>
+        <v>79142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415290</v>
+        <v>415293</v>
       </c>
       <c r="R11" t="n">
-        <v>6971459</v>
+        <v>6971328</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,65 +1688,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784708</t>
+          <t>https://artportalen.se/Sighting/136919523</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6794708</v>
+        <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>106229</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415241</v>
+        <v>415567</v>
       </c>
       <c r="R12" t="n">
-        <v>6971543</v>
+        <v>6971253</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,69 +1790,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794708</t>
+          <t>https://artportalen.se/Sighting/136919529</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6794707</v>
+        <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>103683</v>
+        <v>79142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222002</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>415241</v>
+        <v>415341</v>
       </c>
       <c r="R13" t="n">
-        <v>6971543</v>
+        <v>6971414</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,69 +1892,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794707</t>
+          <t>https://artportalen.se/Sighting/136919562</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6794715</v>
+        <v>135784711</v>
       </c>
       <c r="B14" t="n">
-        <v>104628</v>
+        <v>92267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>415427</v>
+        <v>415319</v>
       </c>
       <c r="R14" t="n">
-        <v>6971592</v>
+        <v>6971444</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,12 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2002,69 +1994,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794715</t>
+          <t>https://artportalen.se/Sighting/135784711</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135784707</v>
+        <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>80050</v>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>415199</v>
+        <v>415307</v>
       </c>
       <c r="R15" t="n">
-        <v>6971418</v>
+        <v>6971311</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2088,12 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,18 +2096,2595 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136919525</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136857485</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91117</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vikavan, Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>415221</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971377</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857485</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136919524</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92166</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>415297</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971323</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919524</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136919531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93436</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>415590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971264</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919531</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135784710</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93386</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>415311</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971457</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784710</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136857956</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vikavan, Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>415209</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971392</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857956</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136919518</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>415276</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971328</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919518</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136919527</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>415559</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971251</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919527</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136919561</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>415353</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6971370</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919561</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136919564</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>415347</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6971412</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919564</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136919513</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>415243</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6971389</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919513</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136857716</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vikavan, Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>415227</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6971388</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857716</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136919515</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93395</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>415254</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6971392</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919515</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136919526</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>415423</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6971297</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919526</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136919560</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>415358</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6971367</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919560</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784712</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>415320</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6971460</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784712</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136919519</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>415273</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6971316</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919519</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135784706</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>415176</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6971428</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Klen gran med helt avskalad bark.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784706</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136919530</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>415581</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6971265</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919530</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135784708</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>415290</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6971459</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784708</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6794708</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794708</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136919532</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>415607</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6971273</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919532</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6794707</v>
+      </c>
+      <c r="B37" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794707</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6794715</v>
+      </c>
+      <c r="B38" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>415427</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6971592</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794715</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135784707</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>415199</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6971418</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784707</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136919528</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>415570</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6971253</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919528</t>
         </is>
       </c>
     </row>
@@ -2139,6 +4704,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92378</v>
+        <v>92379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92379</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136919530</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136919530</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -3881,11 +3881,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vikavan, Hjd</t>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92406</v>
+        <v>92409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92409</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136919530</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92420</v>
+        <v>92423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136919530</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92423</v>
+        <v>92425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92425</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136919530</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136857358</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136858141</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136857485</v>
       </c>
       <c r="B16" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136857956</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919563</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136919514</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136919516</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136919517</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>136919521</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136919522</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136919523</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136919529</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136919525</v>
       </c>
       <c r="B15" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136919524</v>
       </c>
       <c r="B17" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136919531</v>
       </c>
       <c r="B18" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136919518</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>136919527</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136919561</v>
       </c>
       <c r="B23" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136919564</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>136919513</v>
       </c>
       <c r="B25" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136857716</v>
       </c>
       <c r="B26" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136919515</v>
       </c>
       <c r="B27" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>136919526</v>
       </c>
       <c r="B28" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136919519</v>
       </c>
       <c r="B31" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>136919528</v>
       </c>
       <c r="B40" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
